--- a/stories/arbres/ATOM-VIV.ANI.002-03.xlsx
+++ b/stories/arbres/ATOM-VIV.ANI.002-03.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Tom est à la ferme avec papa. Un chat marche. Une chatte le suit. Un chaton dort. Papa dit : trois noms de la famille. Tom répète : chat, chatte, chaton. Près du foin : un chien, une chienne, un chiot. Tom dit les trois noms. Encore : un coq, une poule, un poussin. Tom pose le doigt vers le poussin. Papa dit : le petit, c'est le poussin. Trois noms de la famille, chaque fois.</t>
+          <t>Tom est à la ferme avec papa. Un chat marche. Une chatte le suit. Un chaton dort. Trois noms de la famille. Tom répète : chat, chatte, chaton. Près du foin : un chien, une chienne, un chiot. Tom dit les trois noms. Encore : un coq, une poule, un poussin. Tom pose le doigt vers le poussin. Le petit, c'est le poussin. Trois noms de la famille, chaque fois.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,14 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Tom est à la ferme avec papa. Un chat marche. Une chatte le suit. Un chaton dort.
+papa|Trois noms de la famille.
+narrateur|Tom répète : chat, chatte, chaton. Près du foin : un chien, une chienne, un chiot. Tom dit les trois noms. Encore : un coq, une poule, un poussin. Tom pose le doigt vers le poussin.
+papa|Le petit, c'est le poussin. Trois noms de la famille, chaque fois.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1465,6 +1489,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Le coq, la poule, et le petit. Quel est le petit ?</t>
         </is>
       </c>
     </row>
@@ -1633,6 +1662,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Tom a dit les trois noms. Chat, chatte, chaton. Coq, poule, poussin.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1791,6 +1825,11 @@
         <v>8</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Papa range le seau. Tom salue le chaton.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1953,6 +1992,11 @@
         <v>8</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1971,7 +2015,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1988,6 +2032,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-VIV.ANI.002-03.xlsx
+++ b/stories/arbres/ATOM-VIV.ANI.002-03.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1313,6 +1318,11 @@
 papa|Le petit, c'est le poussin. Trois noms de la famille, chaque fois.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1496,6 +1506,7 @@
           <t>narrateur|Le coq, la poule, et le petit. Quel est le petit ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1667,6 +1678,7 @@
           <t>narrateur|Tom a dit les trois noms. Chat, chatte, chaton. Coq, poule, poussin.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1830,6 +1842,7 @@
           <t>narrateur|Papa range le seau. Tom salue le chaton.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1997,6 +2010,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2015,7 +2029,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2039,6 +2053,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2081,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2240,6 +2268,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-VIV.ANI.002-03.xlsx
+++ b/stories/arbres/ATOM-VIV.ANI.002-03.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Tom dit les trois noms à la ferme</t>
+          <t>Le poulain derrière la barrière</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Mila veut parler au poulain. Cheval et jument sont au pré. La barrière est fermée. Papa l'ouvre avec elle. Le poulain souffle dans sa paume.</t>
         </is>
       </c>
     </row>
@@ -1172,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Tom est à la ferme avec papa. Un chat marche. Une chatte le suit. Un chaton dort. Trois noms de la famille. Tom répète : chat, chatte, chaton. Près du foin : un chien, une chienne, un chiot. Tom dit les trois noms. Encore : un coq, une poule, un poussin. Tom pose le doigt vers le poussin. Le petit, c'est le poussin. Trois noms de la famille, chaque fois.</t>
+          <t>Le portail peint sent encore le soleil. La peinture est chaude sous les doigts. Un peu de poussière blonde vole au vent. Mila vit ici, avec papa. Ses bottes font un bruit mou dans la terre. Papa, je veux voir le poulain. Le petit du pré ? Oui. Je veux lui parler. En ce moment, ils marchent vers le pré. L'herbe sent le foin coupé. Un cheval brun broute près du chêne. Le cheval ! Oui, Mila. Il mange tout calme. Une jument grise gratte le sol. La jument aussi. Tu les vois bien ? Oui. Le poulain est où ? Derrière la barrière, peut-être. La barrière de bois est fermée. Les lattes sentent la résine chaude. Mila pose le front entre deux lattes. Elle ne voit que l'ombre. Je ne le vois pas. On ouvre ensemble ? Oui, papa. Papa soulève le loquet de fer. Mila tient le bois, tout près. La barrière grince un tout petit peu. Dans l'ombre, un poulain avance. Le poulain ! Cheval, jument, poulain. Trois noms de la famille. Le poulain souffle contre la main de Mila. L'air est chaud, un peu humide. Bonjour, petit. Tu lui parles tout doux. Merci d'avoir attendu la barrière. Il sent le foin. La jument s'approche, sans se presser. Elle gratte encore une fois le sol. Elle le garde. Oui. Le petit reste près d'elle. Mila laisse sa main ouverte. Le poil du nez est velours. Ça chatouille. On reste de ce côté du bois ? Oui, papa. Une mouche tourne dans le rai de soleil. Le cheval brun lève un peu la tête. Il nous a vus. Il broute encore. Mila pose l'oreille contre une latte. Le bois sent la résine, et le souffle.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Tom est à la ferme avec papa. Un chat marche. Une chatte le suit. Un chaton dort. Papa dit : &lt;emphasis level="moderate"&gt;trois&lt;/emphasis&gt; noms de la famille. Tom répète : chat, chatte, chaton. Près du foin : un chien, une chienne, un chiot. Tom dit les trois noms. Encore : un coq, une poule, un poussin. Tom pose le doigt vers le poussin. Papa dit : le petit, c'est le poussin. Trois noms de la famille, chaque fois.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>Le portail peint sent encore le soleil. La peinture est chaude sous les doigts. Un peu de poussière blonde vole au vent. Mila vit ici, avec papa. Ses bottes font un bruit mou dans la terre. Papa, je veux voir le poulain. Le petit du pré ? Oui. Je veux lui parler. En ce moment, ils marchent vers le pré. L'herbe sent le foin coupé. Un cheval brun broute près du chêne. Le cheval ! Oui, Mila. Il mange tout calme. Une jument grise gratte le sol. La jument aussi. Tu les vois bien ? Oui. Le poulain est où ? Derrière la barrière, peut-être. La barrière de bois est fermée. Les lattes sentent la résine chaude. Mila pose le front entre deux lattes. Elle ne voit que l'ombre. Je ne le vois pas. On ouvre ensemble ? Oui, papa. Papa soulève le loquet de fer. Mila tient le bois, tout près. La barrière grince un tout petit peu. Dans l'ombre, un poulain avance. Le poulain ! Cheval, jument, poulain. Trois noms de la famille. Le poulain souffle contre la main de Mila. L'air est chaud, un peu humide. Bonjour, petit. Tu lui parles tout doux. Merci d'avoir attendu la barrière. Il sent le foin. La jument s'approche, sans se presser. Elle gratte encore une fois le sol. Elle le garde. Oui. Le petit reste près d'elle. Mila laisse sa main ouverte. Le poil du nez est velours. Ça chatouille. On reste de ce côté du bois ? Oui, papa. Une mouche tourne dans le rai de soleil. Le cheval brun lève un peu la tête. Il nous a vus. Il broute encore. Mila pose l'oreille contre une latte. Le bois sent la résine, et le souffle.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1240,7 +1252,7 @@
         <v>0.92</v>
       </c>
       <c r="AB2" s="2" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
@@ -1312,10 +1324,63 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Tom est à la ferme avec papa. Un chat marche. Une chatte le suit. Un chaton dort.
+          <t>narrateur|Le portail peint sent encore le soleil.
+narrateur|La peinture est chaude sous les doigts.
+narrateur|Un peu de poussière blonde vole au vent.
+narrateur|Mila vit ici, avec papa.
+narrateur|Ses bottes font un bruit mou dans la terre.
+enfant-f|Papa, je veux voir le poulain.
+papa|Le petit du pré ?
+enfant-f|Oui.
+enfant-f|Je veux lui parler.
+narrateur|En ce moment, ils marchent vers le pré.
+narrateur|L'herbe sent le foin coupé.
+narrateur|Un cheval brun broute près du chêne.
+enfant-f|Le cheval !
+papa|Oui, Mila.
+papa|Il mange tout calme.
+narrateur|Une jument grise gratte le sol.
+enfant-f|La jument aussi.
+papa|Tu les vois bien ?
+enfant-f|Oui.
+enfant-f|Le poulain est où ?
+papa|Derrière la barrière, peut-être.
+narrateur|La barrière de bois est fermée.
+narrateur|Les lattes sentent la résine chaude.
+narrateur|Mila pose le front entre deux lattes.
+narrateur|Elle ne voit que l'ombre.
+enfant-f|Je ne le vois pas.
+papa|On ouvre ensemble ?
+enfant-f|Oui, papa.
+narrateur|Papa soulève le loquet de fer.
+narrateur|Mila tient le bois, tout près.
+narrateur|La barrière grince un tout petit peu.
+narrateur|Dans l'ombre, un poulain avance.
+enfant-f|Le poulain !
+papa|Cheval, jument, poulain.
 papa|Trois noms de la famille.
-narrateur|Tom répète : chat, chatte, chaton. Près du foin : un chien, une chienne, un chiot. Tom dit les trois noms. Encore : un coq, une poule, un poussin. Tom pose le doigt vers le poussin.
-papa|Le petit, c'est le poussin. Trois noms de la famille, chaque fois.</t>
+narrateur|Le poulain souffle contre la main de Mila.
+narrateur|L'air est chaud, un peu humide.
+enfant-f|Bonjour, petit.
+papa|Tu lui parles tout doux.
+papa|Merci d'avoir attendu la barrière.
+enfant-f|Il sent le foin.
+narrateur|La jument s'approche, sans se presser.
+narrateur|Elle gratte encore une fois le sol.
+enfant-f|Elle le garde.
+papa|Oui.
+papa|Le petit reste près d'elle.
+narrateur|Mila laisse sa main ouverte.
+narrateur|Le poil du nez est velours.
+enfant-f|Ça chatouille.
+papa|On reste de ce côté du bois ?
+enfant-f|Oui, papa.
+narrateur|Une mouche tourne dans le rai de soleil.
+narrateur|Le cheval brun lève un peu la tête.
+enfant-f|Il nous a vus.
+papa|Il broute encore.
+narrateur|Mila pose l'oreille contre une latte.
+narrateur|Le bois sent la résine, et le souffle.</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
@@ -1347,12 +1412,12 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Le coq, la poule, et le petit. Quel est le petit ?</t>
+          <t>Derrière la barrière, qui attend ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Le coq, la poule, et le petit. Quel est le petit ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Derrière la barrière, qui attend ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1362,12 +1427,12 @@
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>poussin</t>
+          <t>poulain</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>poussin | le poussin | chaton | le petit</t>
+          <t>poulain | le poulain | un poulain</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -1382,7 +1447,7 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>Les trois noms de la famille. Le petit, c'est qui ?</t>
+          <t>C'est le poulain. Qui attend derrière la barrière ?</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr"/>
@@ -1431,7 +1496,7 @@
         <v>0.86</v>
       </c>
       <c r="AB3" s="2" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
@@ -1503,10 +1568,9 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Le coq, la poule, et le petit. Quel est le petit ?</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr"/>
+          <t>narrateur|Derrière la barrière, qui attend ?</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1531,12 +1595,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Tom a dit les trois noms. Chat, chatte, chaton. Coq, poule, poussin.</t>
+          <t>Le poulain reste près de la latte. Sa crinière est courte, encore en brosse. Elle pique un peu. Oui. C'est le petit de la jument. On reste de ce côté ? Oui. Mila laisse sa paume ouverte. Le poulain y pose le nez. Il me parle aussi. Tu entends son souffle ? Oui. Il est chaud. Une paille blonde colle à sa botte. On la laisse au pré. Le poulain recule d'un pas, puis revient.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Tom a dit les &lt;emphasis level="moderate"&gt;trois&lt;/emphasis&gt; noms. Chat, chatte, chaton. Coq, poule, poussin.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Le poulain reste près de la latte. Sa crinière est courte, encore en brosse. Elle pique un peu. Oui. C'est le petit de la jument. On reste de ce côté ? Oui. Mila laisse sa paume ouverte. Le poulain y pose le nez. Il me parle aussi. Tu entends son souffle ? Oui. Il est chaud. Une paille blonde colle à sa botte. On la laisse au pré. Le poulain recule d'un pas, puis revient.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1599,7 +1663,7 @@
         <v>0.92</v>
       </c>
       <c r="AB4" s="2" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
@@ -1675,10 +1739,24 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Tom a dit les trois noms. Chat, chatte, chaton. Coq, poule, poussin.</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr"/>
+          <t>narrateur|Le poulain reste près de la latte.
+narrateur|Sa crinière est courte, encore en brosse.
+enfant-f|Elle pique un peu.
+papa|Oui.
+papa|C'est le petit de la jument.
+papa|On reste de ce côté ?
+enfant-f|Oui.
+narrateur|Mila laisse sa paume ouverte.
+narrateur|Le poulain y pose le nez.
+enfant-f|Il me parle aussi.
+papa|Tu entends son souffle ?
+enfant-f|Oui.
+enfant-f|Il est chaud.
+narrateur|Une paille blonde colle à sa botte.
+papa|On la laisse au pré.
+narrateur|Le poulain recule d'un pas, puis revient.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1703,12 +1781,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Papa range le seau. Tom salue le chaton.</t>
+          <t>Papa referme le loquet, tout doux. La barrière retrouve son bois chaud. Le cheval broute encore. La jument aussi. Tu as vu les trois ? Cheval, jument, poulain. Mila garde l'odeur du souffle dans la main. Tes doigts sentent le pré. Et le poulain. Le loquet de fer est redevenu froid.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Papa range le seau. Tom salue le chaton.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Papa referme le loquet, tout doux. La barrière retrouve son bois chaud. Le cheval broute encore. La jument aussi. Tu as vu les trois ? Cheval, jument, poulain. Mila garde l'odeur du souffle dans la main. Tes doigts sentent le pré. Et le poulain. Le loquet de fer est redevenu froid.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1771,7 +1849,7 @@
         <v>0.92</v>
       </c>
       <c r="AB5" s="2" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
@@ -1839,10 +1917,18 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Papa range le seau. Tom salue le chaton.</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr"/>
+          <t>narrateur|Papa referme le loquet, tout doux.
+narrateur|La barrière retrouve son bois chaud.
+enfant-f|Le cheval broute encore.
+papa|La jument aussi.
+papa|Tu as vu les trois ?
+enfant-f|Cheval, jument, poulain.
+narrateur|Mila garde l'odeur du souffle dans la main.
+papa|Tes doigts sentent le pré.
+enfant-f|Et le poulain.
+narrateur|Le loquet de fer est redevenu froid.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1867,12 +1953,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Il a soufflé, papa. Dans ta paume. Le poulain souffle encore contre le bois.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>Il a soufflé, papa. Dans ta paume. Le poulain souffle encore contre le bois.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -1928,14 +2014,14 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="AA6" s="2" t="n">
         <v>0.88</v>
       </c>
       <c r="AB6" s="2" t="n">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
@@ -2007,10 +2093,11 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+          <t>enfant-f|Il a soufflé, papa.
+papa|Dans ta paume.
+narrateur|Le poulain souffle encore contre le bois.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2029,7 +2116,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2067,6 +2154,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-VIV.ANI.002-03.xlsx
+++ b/stories/arbres/ATOM-VIV.ANI.002-03.xlsx
@@ -671,7 +671,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>ferme</t>
+          <t>ferme, pré, barrière de bois</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Tom, papa</t>
+          <t>Mila, papa</t>
         </is>
       </c>
     </row>
